--- a/Vrindavanam Glassmorphism/Vrindavanam/coffee.xlsx
+++ b/Vrindavanam Glassmorphism/Vrindavanam/coffee.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Glassmorphism\Vrindavanam Glassmorphism\Vrindavanam\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{073B3BBF-58BD-4E90-8ADF-56F35052043D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5A1319-1AF3-4EBA-B369-0476BE235C3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{BD9E1797-03AD-478C-9B78-DB540EFC9CA1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BD9E1797-03AD-478C-9B78-DB540EFC9CA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="36">
   <si>
     <t>serial_no</t>
   </si>
@@ -126,17 +126,38 @@
     <t>Natural</t>
   </si>
   <si>
-    <t>Aroma rich</t>
+    <t>50gm</t>
+  </si>
+  <si>
+    <t>100gm</t>
+  </si>
+  <si>
+    <t>250gm</t>
+  </si>
+  <si>
+    <t>1kg</t>
+  </si>
+  <si>
+    <t>Out Of Stock</t>
+  </si>
+  <si>
+    <t>Pure</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -479,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBA63B6-2881-429C-AD8E-0392E8073FB3}">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" customWidth="1"/>
@@ -559,7 +580,7 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
         <v>23</v>
@@ -568,7 +589,7 @@
         <v>46171</v>
       </c>
       <c r="I2">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -583,7 +604,7 @@
         <v>28</v>
       </c>
       <c r="N2">
-        <v>1200</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -594,25 +615,25 @@
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="G3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="I3">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -624,10 +645,10 @@
         <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N3">
-        <v>2100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
@@ -638,28 +659,28 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="I4">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="s">
         <v>26</v>
@@ -668,13 +689,542 @@
         <v>27</v>
       </c>
       <c r="M4" t="s">
+        <v>28</v>
+      </c>
+      <c r="N4">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="1">
+        <v>46171</v>
+      </c>
+      <c r="I5">
+        <v>400</v>
+      </c>
+      <c r="J5">
+        <v>4</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N5">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="1">
+        <v>46171</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6">
+        <v>4</v>
+      </c>
+      <c r="K6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L6" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c r="N4">
-        <v>3200</v>
+      <c r="G7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I7">
+        <v>100</v>
+      </c>
+      <c r="J7">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I8">
+        <v>200</v>
+      </c>
+      <c r="J8">
+        <v>3</v>
+      </c>
+      <c r="K8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H9" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I9">
+        <v>300</v>
+      </c>
+      <c r="J9">
+        <v>3</v>
+      </c>
+      <c r="K9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I10">
+        <v>400</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10" t="s">
+        <v>26</v>
+      </c>
+      <c r="L10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="1">
+        <v>46172</v>
+      </c>
+      <c r="I11">
+        <v>500</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M11" t="s">
+        <v>29</v>
+      </c>
+      <c r="N11">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I12">
+        <v>100</v>
+      </c>
+      <c r="J12">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L12" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I13">
+        <v>200</v>
+      </c>
+      <c r="J13">
+        <v>3</v>
+      </c>
+      <c r="K13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L13" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H14" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I14">
+        <v>300</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I15">
+        <v>400</v>
+      </c>
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M15" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1">
+        <v>46174</v>
+      </c>
+      <c r="I16">
+        <v>500</v>
+      </c>
+      <c r="J16">
+        <v>4</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" t="s">
+        <v>35</v>
+      </c>
+      <c r="N16">
+        <v>2000</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>